--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/64.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/64.xlsx
@@ -426,13 +426,13 @@
         <v>-21.54363711428892</v>
       </c>
       <c r="E2">
-        <v>-10.12157168888158</v>
+        <v>-8.195475839199146</v>
       </c>
       <c r="F2">
-        <v>-0.9915584135007244</v>
+        <v>-1.077480822356103</v>
       </c>
       <c r="G2">
-        <v>-11.26241417490367</v>
+        <v>-8.848020070931032</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.36714083822757</v>
       </c>
       <c r="E3">
-        <v>-9.533667079309783</v>
+        <v>-8.892186093753239</v>
       </c>
       <c r="F3">
-        <v>-0.9666460922289321</v>
+        <v>-0.7803396364001008</v>
       </c>
       <c r="G3">
-        <v>-11.19110502398776</v>
+        <v>-9.441832624310106</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.04188913973904</v>
       </c>
       <c r="E4">
-        <v>-10.43893620428713</v>
+        <v>-9.825789880596583</v>
       </c>
       <c r="F4">
-        <v>-1.066485901818745</v>
+        <v>-0.8307491063300619</v>
       </c>
       <c r="G4">
-        <v>-10.90859299930298</v>
+        <v>-8.662447440727187</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.59940519654561</v>
       </c>
       <c r="E5">
-        <v>-12.06176014967588</v>
+        <v>-9.735003033690807</v>
       </c>
       <c r="F5">
-        <v>-0.473483357544066</v>
+        <v>-1.107967227881333</v>
       </c>
       <c r="G5">
-        <v>-9.534964891420882</v>
+        <v>-8.546091696658422</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.02924800894347</v>
       </c>
       <c r="E6">
-        <v>-12.77406194023838</v>
+        <v>-11.58045581824465</v>
       </c>
       <c r="F6">
-        <v>-0.6436971198387111</v>
+        <v>-0.8441471207029412</v>
       </c>
       <c r="G6">
-        <v>-9.764872347486648</v>
+        <v>-7.954374718605707</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.37044814644577</v>
       </c>
       <c r="E7">
-        <v>-11.94489382095993</v>
+        <v>-11.66757912967822</v>
       </c>
       <c r="F7">
-        <v>-0.7696056515946248</v>
+        <v>-0.8064199557098405</v>
       </c>
       <c r="G7">
-        <v>-9.807836607495309</v>
+        <v>-8.330826783512851</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.66622518423506</v>
       </c>
       <c r="E8">
-        <v>-13.34736222113544</v>
+        <v>-11.85154838623983</v>
       </c>
       <c r="F8">
-        <v>-0.8909457371240992</v>
+        <v>-0.4745635486373165</v>
       </c>
       <c r="G8">
-        <v>-8.906567068793043</v>
+        <v>-8.552338696091025</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.96932088033266</v>
       </c>
       <c r="E9">
-        <v>-12.48258671073468</v>
+        <v>-13.27410509711336</v>
       </c>
       <c r="F9">
-        <v>-0.7150005007694842</v>
+        <v>-0.7023364199154853</v>
       </c>
       <c r="G9">
-        <v>-9.124649256192532</v>
+        <v>-6.808479038370075</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.35793669240396</v>
       </c>
       <c r="E10">
-        <v>-15.09420295569825</v>
+        <v>-13.53081976013419</v>
       </c>
       <c r="F10">
-        <v>-0.378868889531112</v>
+        <v>-0.6089321966780216</v>
       </c>
       <c r="G10">
-        <v>-8.352547272796009</v>
+        <v>-6.90443520082585</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.86769878099056</v>
       </c>
       <c r="E11">
-        <v>-15.12287725311482</v>
+        <v>-13.52930724981562</v>
       </c>
       <c r="F11">
-        <v>-0.4701806567091044</v>
+        <v>-0.7671942740850755</v>
       </c>
       <c r="G11">
-        <v>-8.889858745456342</v>
+        <v>-6.415371618854858</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.57055052814655</v>
       </c>
       <c r="E12">
-        <v>-14.67172803010066</v>
+        <v>-14.52574361351539</v>
       </c>
       <c r="F12">
-        <v>-0.04127520982679872</v>
+        <v>-0.7190023436924087</v>
       </c>
       <c r="G12">
-        <v>-7.65828945720991</v>
+        <v>-5.754570176488632</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.46169023628476</v>
       </c>
       <c r="E13">
-        <v>-15.89615947466461</v>
+        <v>-14.70056988105551</v>
       </c>
       <c r="F13">
-        <v>-0.1582729934307981</v>
+        <v>-0.9962428311635556</v>
       </c>
       <c r="G13">
-        <v>-8.384977376898711</v>
+        <v>-5.744552465686797</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.57153154899217</v>
       </c>
       <c r="E14">
-        <v>-16.79853037627705</v>
+        <v>-16.12765506593672</v>
       </c>
       <c r="F14">
-        <v>0.02704770518870171</v>
+        <v>-0.2782189366213609</v>
       </c>
       <c r="G14">
-        <v>-7.052707914438728</v>
+        <v>-5.11137752584579</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.86604990965559</v>
       </c>
       <c r="E15">
-        <v>-18.51024373796237</v>
+        <v>-15.99714897350967</v>
       </c>
       <c r="F15">
-        <v>0.2322749008648764</v>
+        <v>0.3643092095644924</v>
       </c>
       <c r="G15">
-        <v>-7.625660720374853</v>
+        <v>-5.312301155715237</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.32245450280649</v>
       </c>
       <c r="E16">
-        <v>-19.16715776293705</v>
+        <v>-17.88293687604983</v>
       </c>
       <c r="F16">
-        <v>0.3241748088988564</v>
+        <v>0.2538331625227336</v>
       </c>
       <c r="G16">
-        <v>-6.776065486995071</v>
+        <v>-4.60762836386259</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.89077641795797</v>
       </c>
       <c r="E17">
-        <v>-19.40533285337047</v>
+        <v>-17.9785601331958</v>
       </c>
       <c r="F17">
-        <v>0.9494638010650492</v>
+        <v>0.8177136223845934</v>
       </c>
       <c r="G17">
-        <v>-5.73414079996579</v>
+        <v>-4.946290551438953</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.5089945024319</v>
       </c>
       <c r="E18">
-        <v>-19.61891380146823</v>
+        <v>-19.57792658322481</v>
       </c>
       <c r="F18">
-        <v>1.587911409424712</v>
+        <v>0.8610587751034804</v>
       </c>
       <c r="G18">
-        <v>-6.268244353998567</v>
+        <v>-4.789009843413718</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.13052623467193</v>
       </c>
       <c r="E19">
-        <v>-21.29002486520077</v>
+        <v>-18.74195669598684</v>
       </c>
       <c r="F19">
-        <v>1.356964234259016</v>
+        <v>1.41042540970089</v>
       </c>
       <c r="G19">
-        <v>-6.648692247371612</v>
+        <v>-4.999106994972486</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.68075021169369</v>
       </c>
       <c r="E20">
-        <v>-22.26542646713492</v>
+        <v>-20.16447265059431</v>
       </c>
       <c r="F20">
-        <v>1.540790558083865</v>
+        <v>1.567530257846233</v>
       </c>
       <c r="G20">
-        <v>-7.026776411229617</v>
+        <v>-5.046182952540923</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-20.13539070886183</v>
       </c>
       <c r="E21">
-        <v>-22.62473823727352</v>
+        <v>-22.44748017919128</v>
       </c>
       <c r="F21">
-        <v>1.762059088515252</v>
+        <v>1.856282567114085</v>
       </c>
       <c r="G21">
-        <v>-8.127350723032627</v>
+        <v>-5.112367378962032</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.43334589231144</v>
       </c>
       <c r="E22">
-        <v>-23.05402851625265</v>
+        <v>-20.99624917090118</v>
       </c>
       <c r="F22">
-        <v>2.000193179267638</v>
+        <v>2.375112265774693</v>
       </c>
       <c r="G22">
-        <v>-6.846186152062374</v>
+        <v>-5.258554448885169</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-20.57089794981483</v>
       </c>
       <c r="E23">
-        <v>-23.04250807837714</v>
+        <v>-22.32160671567408</v>
       </c>
       <c r="F23">
-        <v>1.993617598824215</v>
+        <v>2.533824146681467</v>
       </c>
       <c r="G23">
-        <v>-6.802162517481146</v>
+        <v>-5.412554406280987</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-20.52007067002389</v>
       </c>
       <c r="E24">
-        <v>-22.81745650561795</v>
+        <v>-22.52278870193884</v>
       </c>
       <c r="F24">
-        <v>2.528583894491358</v>
+        <v>3.020057588041916</v>
       </c>
       <c r="G24">
-        <v>-7.205022804155056</v>
+        <v>-5.14149355861654</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-20.29258928811157</v>
       </c>
       <c r="E25">
-        <v>-24.07287176934238</v>
+        <v>-22.24414263929886</v>
       </c>
       <c r="F25">
-        <v>2.285038907863886</v>
+        <v>2.723581581110361</v>
       </c>
       <c r="G25">
-        <v>-7.176419690695753</v>
+        <v>-5.946191173392727</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.90412615928604</v>
       </c>
       <c r="E26">
-        <v>-22.29691294691025</v>
+        <v>-23.03698786856179</v>
       </c>
       <c r="F26">
-        <v>2.117211672056706</v>
+        <v>2.380741850644119</v>
       </c>
       <c r="G26">
-        <v>-6.757576090158241</v>
+        <v>-5.703438800634588</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-19.38444403592536</v>
       </c>
       <c r="E27">
-        <v>-23.61915943003988</v>
+        <v>-22.47874929221424</v>
       </c>
       <c r="F27">
-        <v>2.197453965631089</v>
+        <v>2.628930664931684</v>
       </c>
       <c r="G27">
-        <v>-6.414004363547138</v>
+        <v>-5.937914809544549</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.78801011694494</v>
       </c>
       <c r="E28">
-        <v>-23.80713185762427</v>
+        <v>-22.8951243633235</v>
       </c>
       <c r="F28">
-        <v>2.135899640663864</v>
+        <v>2.536882479132603</v>
       </c>
       <c r="G28">
-        <v>-7.745767312539612</v>
+        <v>-5.532793420267316</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.14748101417732</v>
       </c>
       <c r="E29">
-        <v>-24.61939518343208</v>
+        <v>-22.88742142903645</v>
       </c>
       <c r="F29">
-        <v>1.780597950989905</v>
+        <v>2.343521646501531</v>
       </c>
       <c r="G29">
-        <v>-7.679106167560848</v>
+        <v>-6.086048480244777</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.5325678064932</v>
       </c>
       <c r="E30">
-        <v>-23.10858304262306</v>
+        <v>-22.28926435431129</v>
       </c>
       <c r="F30">
-        <v>2.138472549816959</v>
+        <v>2.202415886373858</v>
       </c>
       <c r="G30">
-        <v>-6.999404820710923</v>
+        <v>-5.609551729140858</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.96010521442484</v>
       </c>
       <c r="E31">
-        <v>-22.8678493643753</v>
+        <v>-21.80868005024728</v>
       </c>
       <c r="F31">
-        <v>1.60551090326459</v>
+        <v>2.325759792650705</v>
       </c>
       <c r="G31">
-        <v>-6.023611591374123</v>
+        <v>-5.786632810036473</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.48315534638872</v>
       </c>
       <c r="E32">
-        <v>-22.69915465064157</v>
+        <v>-21.84829061239237</v>
       </c>
       <c r="F32">
-        <v>1.793545333495661</v>
+        <v>2.152486869537521</v>
       </c>
       <c r="G32">
-        <v>-6.733329654628619</v>
+        <v>-4.935392235523673</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.10080296377865</v>
       </c>
       <c r="E33">
-        <v>-21.19456463311908</v>
+        <v>-20.99011308862078</v>
       </c>
       <c r="F33">
-        <v>1.846370322772186</v>
+        <v>1.86612854206376</v>
       </c>
       <c r="G33">
-        <v>-6.443084195564096</v>
+        <v>-4.451261366406194</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.82848114312592</v>
       </c>
       <c r="E34">
-        <v>-22.0677585767001</v>
+        <v>-20.76527435413995</v>
       </c>
       <c r="F34">
-        <v>1.792458515463188</v>
+        <v>2.105780201898074</v>
       </c>
       <c r="G34">
-        <v>-6.52719522608036</v>
+        <v>-4.024214234022367</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.65458512612455</v>
       </c>
       <c r="E35">
-        <v>-22.04799631613063</v>
+        <v>-19.84816779810655</v>
       </c>
       <c r="F35">
-        <v>1.09721472449798</v>
+        <v>1.771366624653107</v>
       </c>
       <c r="G35">
-        <v>-6.436519383759721</v>
+        <v>-3.917055185461699</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.55969442443165</v>
       </c>
       <c r="E36">
-        <v>-21.29914068337822</v>
+        <v>-20.42615957807556</v>
       </c>
       <c r="F36">
-        <v>1.41537573330002</v>
+        <v>2.16052037660987</v>
       </c>
       <c r="G36">
-        <v>-4.878278703880166</v>
+        <v>-3.978224135390812</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-15.52933264537598</v>
       </c>
       <c r="E37">
-        <v>-21.32175588257252</v>
+        <v>-19.75939159366018</v>
       </c>
       <c r="F37">
-        <v>1.620618667956848</v>
+        <v>1.652534007251907</v>
       </c>
       <c r="G37">
-        <v>-6.222207907729462</v>
+        <v>-3.621506232443263</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-15.52086137107285</v>
       </c>
       <c r="E38">
-        <v>-21.09357513427403</v>
+        <v>-18.5112671730881</v>
       </c>
       <c r="F38">
-        <v>1.323972017340317</v>
+        <v>1.43870421609766</v>
       </c>
       <c r="G38">
-        <v>-5.818112787569403</v>
+        <v>-3.433079911984565</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-15.52740269126024</v>
       </c>
       <c r="E39">
-        <v>-20.1559047777718</v>
+        <v>-19.26578792682411</v>
       </c>
       <c r="F39">
-        <v>1.250745995667646</v>
+        <v>1.47243368000485</v>
       </c>
       <c r="G39">
-        <v>-6.039187708136394</v>
+        <v>-2.58962905112567</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-15.50400379417819</v>
       </c>
       <c r="E40">
-        <v>-20.21756447986024</v>
+        <v>-18.49314874858341</v>
       </c>
       <c r="F40">
-        <v>1.147470118091021</v>
+        <v>1.552155758850274</v>
       </c>
       <c r="G40">
-        <v>-4.000043941040149</v>
+        <v>-3.245312390088182</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-15.45610229645853</v>
       </c>
       <c r="E41">
-        <v>-20.03950941035264</v>
+        <v>-18.10384036661799</v>
       </c>
       <c r="F41">
-        <v>1.504746635653253</v>
+        <v>1.603738197022599</v>
       </c>
       <c r="G41">
-        <v>-4.815596834639606</v>
+        <v>-2.594379683974524</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-15.35882869000613</v>
       </c>
       <c r="E42">
-        <v>-19.37501471988912</v>
+        <v>-16.74261277923034</v>
       </c>
       <c r="F42">
-        <v>1.232629600568421</v>
+        <v>1.288019215324013</v>
       </c>
       <c r="G42">
-        <v>-4.345565578973883</v>
+        <v>-3.091362090875454</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-15.22199408974748</v>
       </c>
       <c r="E43">
-        <v>-19.26480524796445</v>
+        <v>-16.3671026575663</v>
       </c>
       <c r="F43">
-        <v>1.144971762004177</v>
+        <v>1.399795799188167</v>
       </c>
       <c r="G43">
-        <v>-4.111198818066718</v>
+        <v>-3.283052609235874</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-15.04663176859038</v>
       </c>
       <c r="E44">
-        <v>-19.21121981503168</v>
+        <v>-16.76287317194066</v>
       </c>
       <c r="F44">
-        <v>0.9813841105645253</v>
+        <v>1.42578831155321</v>
       </c>
       <c r="G44">
-        <v>-4.218579673178518</v>
+        <v>-1.961082253948564</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.84419996911947</v>
       </c>
       <c r="E45">
-        <v>-18.57725156785386</v>
+        <v>-15.59292379816299</v>
       </c>
       <c r="F45">
-        <v>0.9181183785431158</v>
+        <v>1.490255176308678</v>
       </c>
       <c r="G45">
-        <v>-4.27880842817448</v>
+        <v>-2.318220596179601</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.6388681252306</v>
       </c>
       <c r="E46">
-        <v>-17.06235927196393</v>
+        <v>-14.41523073383221</v>
       </c>
       <c r="F46">
-        <v>0.6825911600073409</v>
+        <v>1.716985961394126</v>
       </c>
       <c r="G46">
-        <v>-4.887614442300912</v>
+        <v>-1.60529792484309</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.4363026397645</v>
       </c>
       <c r="E47">
-        <v>-15.43627029681565</v>
+        <v>-14.34427860308003</v>
       </c>
       <c r="F47">
-        <v>0.8463088651292323</v>
+        <v>1.198300398661604</v>
       </c>
       <c r="G47">
-        <v>-4.644180097161683</v>
+        <v>-2.846947824256602</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.2718287303879</v>
       </c>
       <c r="E48">
-        <v>-15.62393931664152</v>
+        <v>-14.31192265629522</v>
       </c>
       <c r="F48">
-        <v>0.9880673787703117</v>
+        <v>1.082892252103577</v>
       </c>
       <c r="G48">
-        <v>-4.787228769913591</v>
+        <v>-2.336498118101917</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.13973597861757</v>
       </c>
       <c r="E49">
-        <v>-16.27167412480266</v>
+        <v>-13.65439275885549</v>
       </c>
       <c r="F49">
-        <v>0.6393039930066499</v>
+        <v>1.195727489508509</v>
       </c>
       <c r="G49">
-        <v>-5.167223118547756</v>
+        <v>-2.696629193500454</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.07174721175273</v>
       </c>
       <c r="E50">
-        <v>-15.23789143596163</v>
+        <v>-13.65960956091233</v>
       </c>
       <c r="F50">
-        <v>0.8711648574176343</v>
+        <v>1.355209752099886</v>
       </c>
       <c r="G50">
-        <v>-3.9916351553704</v>
+        <v>-2.907855241088113</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.05668094664729</v>
       </c>
       <c r="E51">
-        <v>-15.10147115648056</v>
+        <v>-13.12702931829224</v>
       </c>
       <c r="F51">
-        <v>0.8951676312811528</v>
+        <v>1.044929830768081</v>
       </c>
       <c r="G51">
-        <v>-4.423694453700683</v>
+        <v>-2.271081738245918</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.10886142799542</v>
       </c>
       <c r="E52">
-        <v>-14.69728220892595</v>
+        <v>-12.19471161806708</v>
       </c>
       <c r="F52">
-        <v>0.6606800138358911</v>
+        <v>0.5820348126141061</v>
       </c>
       <c r="G52">
-        <v>-4.661888205251245</v>
+        <v>-2.94520812640771</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.22026778598917</v>
       </c>
       <c r="E53">
-        <v>-13.56063976147469</v>
+        <v>-12.39385126255438</v>
       </c>
       <c r="F53">
-        <v>0.4490735607907574</v>
+        <v>0.6951019928918218</v>
       </c>
       <c r="G53">
-        <v>-4.171748695979988</v>
+        <v>-3.464050065504447</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.38563230955609</v>
       </c>
       <c r="E54">
-        <v>-14.02199163642813</v>
+        <v>-11.96329753932711</v>
       </c>
       <c r="F54">
-        <v>0.5632664923688777</v>
+        <v>0.8990675850135329</v>
       </c>
       <c r="G54">
-        <v>-5.664308152360403</v>
+        <v>-2.951882186214881</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.60251480911918</v>
       </c>
       <c r="E55">
-        <v>-13.8130342602922</v>
+        <v>-12.21486332740121</v>
       </c>
       <c r="F55">
-        <v>1.46216026747533</v>
+        <v>0.6968730423990072</v>
       </c>
       <c r="G55">
-        <v>-5.27272358379325</v>
+        <v>-3.765703664497299</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.84731087782517</v>
       </c>
       <c r="E56">
-        <v>-13.01932409249381</v>
+        <v>-11.36000517507725</v>
       </c>
       <c r="F56">
-        <v>0.7095570040706731</v>
+        <v>0.7559256978097783</v>
       </c>
       <c r="G56">
-        <v>-5.518630906450314</v>
+        <v>-3.402755314844841</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.12469653879088</v>
       </c>
       <c r="E57">
-        <v>-12.97298874644733</v>
+        <v>-11.34271546131596</v>
       </c>
       <c r="F57">
-        <v>0.5178827274717012</v>
+        <v>0.375412646231617</v>
       </c>
       <c r="G57">
-        <v>-5.672213735108182</v>
+        <v>-3.983494523889332</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.4007121865274</v>
       </c>
       <c r="E58">
-        <v>-11.62904634434695</v>
+        <v>-10.7119126174695</v>
       </c>
       <c r="F58">
-        <v>0.8690707446233572</v>
+        <v>0.8719236419585986</v>
       </c>
       <c r="G58">
-        <v>-5.826170655411989</v>
+        <v>-3.533680769831938</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.68456897131479</v>
       </c>
       <c r="E59">
-        <v>-11.28513591430843</v>
+        <v>-10.60781205698118</v>
       </c>
       <c r="F59">
-        <v>0.1458380758523592</v>
+        <v>0.7419958715643018</v>
       </c>
       <c r="G59">
-        <v>-6.321924849917849</v>
+        <v>-4.117684176778151</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.94726963669114</v>
       </c>
       <c r="E60">
-        <v>-11.35393249143296</v>
+        <v>-10.00311133731493</v>
       </c>
       <c r="F60">
-        <v>0.3228792422808779</v>
+        <v>0.8557373429078964</v>
       </c>
       <c r="G60">
-        <v>-6.56439582630515</v>
+        <v>-4.295069827863379</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.19364389973596</v>
       </c>
       <c r="E61">
-        <v>-11.90304619265505</v>
+        <v>-9.868289609158568</v>
       </c>
       <c r="F61">
-        <v>1.134726513966353</v>
+        <v>0.7781425115528611</v>
       </c>
       <c r="G61">
-        <v>-6.643206673413039</v>
+        <v>-4.850874007906079</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.41085879796639</v>
       </c>
       <c r="E62">
-        <v>-11.82643346939328</v>
+        <v>-10.33727196281493</v>
       </c>
       <c r="F62">
-        <v>0.2192629057017018</v>
+        <v>0.7337436754976131</v>
       </c>
       <c r="G62">
-        <v>-7.937666395269006</v>
+        <v>-4.321842209639465</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.59808674856227</v>
       </c>
       <c r="E63">
-        <v>-12.06472630015091</v>
+        <v>-9.277174311515335</v>
       </c>
       <c r="F63">
-        <v>0.1536007067839934</v>
+        <v>0.7879868297677304</v>
       </c>
       <c r="G63">
-        <v>-7.185771981844194</v>
+        <v>-5.230457848893375</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.76152027533957</v>
       </c>
       <c r="E64">
-        <v>-11.95757354818141</v>
+        <v>-9.481947377668179</v>
       </c>
       <c r="F64">
-        <v>0.3024757247825233</v>
+        <v>0.3876352072599237</v>
       </c>
       <c r="G64">
-        <v>-6.637406597628236</v>
+        <v>-5.100449415020655</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.89369079410659</v>
       </c>
       <c r="E65">
-        <v>-11.50790060769375</v>
+        <v>-9.990132730808947</v>
       </c>
       <c r="F65">
-        <v>0.388848765505025</v>
+        <v>0.7841945637977142</v>
       </c>
       <c r="G65">
-        <v>-8.366997804074929</v>
+        <v>-5.430083744911427</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.01706451008483</v>
       </c>
       <c r="E66">
-        <v>-10.67611050196486</v>
+        <v>-9.162386552368906</v>
       </c>
       <c r="F66">
-        <v>0.2331248058201487</v>
+        <v>0.8911566763167976</v>
       </c>
       <c r="G66">
-        <v>-6.641951976653655</v>
+        <v>-5.00604258787726</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.11608709028726</v>
       </c>
       <c r="E67">
-        <v>-10.85822308418332</v>
+        <v>-9.646783831547381</v>
       </c>
       <c r="F67">
-        <v>0.3208041819368652</v>
+        <v>0.2978915395754309</v>
       </c>
       <c r="G67">
-        <v>-6.727950018127303</v>
+        <v>-5.991472815278878</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.21938660964012</v>
       </c>
       <c r="E68">
-        <v>-10.99976053929306</v>
+        <v>-9.427429079089837</v>
       </c>
       <c r="F68">
-        <v>0.4489211411886423</v>
+        <v>0.45078165437533</v>
       </c>
       <c r="G68">
-        <v>-7.29476507263362</v>
+        <v>-5.660011064250429</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.31217249328227</v>
       </c>
       <c r="E69">
-        <v>-10.00194299102095</v>
+        <v>-8.696927351490508</v>
       </c>
       <c r="F69">
-        <v>0.5123467481187921</v>
+        <v>0.4023519825380597</v>
       </c>
       <c r="G69">
-        <v>-7.154937560691423</v>
+        <v>-5.569788766668672</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.41253649860938</v>
       </c>
       <c r="E70">
-        <v>-10.65961779962893</v>
+        <v>-8.913900126620018</v>
       </c>
       <c r="F70">
-        <v>0.5054679852059449</v>
+        <v>0.4893197910557714</v>
       </c>
       <c r="G70">
-        <v>-7.708030403937459</v>
+        <v>-5.676044036297119</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.51149559843642</v>
       </c>
       <c r="E71">
-        <v>-11.02955789826353</v>
+        <v>-8.80589602153708</v>
       </c>
       <c r="F71">
-        <v>0.3281650546781416</v>
+        <v>0.1571229249806969</v>
       </c>
       <c r="G71">
-        <v>-7.313294196016921</v>
+        <v>-5.676729319223749</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.60964445146809</v>
       </c>
       <c r="E72">
-        <v>-10.34612965797394</v>
+        <v>-9.150761959591216</v>
       </c>
       <c r="F72">
-        <v>-0.05307696021448328</v>
+        <v>0.6911705611981354</v>
       </c>
       <c r="G72">
-        <v>-7.566812462868769</v>
+        <v>-5.976492596713676</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.70856369937052</v>
       </c>
       <c r="E73">
-        <v>-10.86038316628498</v>
+        <v>-9.500948854604365</v>
       </c>
       <c r="F73">
-        <v>-0.03783500000297237</v>
+        <v>0.3985530896288212</v>
       </c>
       <c r="G73">
-        <v>-7.03616842892453</v>
+        <v>-5.340937374629933</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.79472437337417</v>
       </c>
       <c r="E74">
-        <v>-12.23376064943522</v>
+        <v>-9.013259374822313</v>
       </c>
       <c r="F74">
-        <v>0.267841683671476</v>
+        <v>0.5593889045563732</v>
       </c>
       <c r="G74">
-        <v>-6.920885301610489</v>
+        <v>-4.996428763631216</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.88373577045692</v>
       </c>
       <c r="E75">
-        <v>-11.24868622702069</v>
+        <v>-9.046376105240407</v>
       </c>
       <c r="F75">
-        <v>0.5007380073359597</v>
+        <v>0.3957175880090385</v>
       </c>
       <c r="G75">
-        <v>-7.17580061867991</v>
+        <v>-5.496403903699647</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.95179028918653</v>
       </c>
       <c r="E76">
-        <v>-12.21278022935768</v>
+        <v>-9.676209855649223</v>
       </c>
       <c r="F76">
-        <v>0.4441845363794347</v>
+        <v>0.2514300686872122</v>
       </c>
       <c r="G76">
-        <v>-6.306229553516165</v>
+        <v>-5.517631121697454</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.02245572414393</v>
       </c>
       <c r="E77">
-        <v>-11.21540647153832</v>
+        <v>-11.463766100015</v>
       </c>
       <c r="F77">
-        <v>0.4308660452772243</v>
+        <v>0.4051460657877025</v>
       </c>
       <c r="G77">
-        <v>-7.567348771246131</v>
+        <v>-5.794601293149499</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-18.07244676327081</v>
       </c>
       <c r="E78">
-        <v>-11.93996684123959</v>
+        <v>-10.89984881726183</v>
       </c>
       <c r="F78">
-        <v>-0.182881303865763</v>
+        <v>0.07392584488052853</v>
       </c>
       <c r="G78">
-        <v>-7.191562125992379</v>
+        <v>-4.606638510746348</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-18.11691941366944</v>
       </c>
       <c r="E79">
-        <v>-13.57663433166979</v>
+        <v>-10.86509277925296</v>
       </c>
       <c r="F79">
-        <v>-0.4273143003490355</v>
+        <v>0.3349054802347212</v>
       </c>
       <c r="G79">
-        <v>-6.883972718847615</v>
+        <v>-5.221466407208714</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-18.14317099026015</v>
       </c>
       <c r="E80">
-        <v>-13.78184665980138</v>
+        <v>-12.41696006541552</v>
       </c>
       <c r="F80">
-        <v>-0.184554606019418</v>
+        <v>0.03735093894472195</v>
       </c>
       <c r="G80">
-        <v>-7.906580372655249</v>
+        <v>-5.708093427662804</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-18.15256166217921</v>
       </c>
       <c r="E81">
-        <v>-13.24410848528655</v>
+        <v>-11.45185168490082</v>
       </c>
       <c r="F81">
-        <v>-0.175485639693569</v>
+        <v>-0.2031274315575857</v>
       </c>
       <c r="G81">
-        <v>-6.284002550765498</v>
+        <v>-4.295275081686814</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-18.1459209150626</v>
       </c>
       <c r="E82">
-        <v>-16.45291271153765</v>
+        <v>-12.10155185078128</v>
       </c>
       <c r="F82">
-        <v>-0.01552458074337329</v>
+        <v>-0.1410396379829572</v>
       </c>
       <c r="G82">
-        <v>-7.912625428809958</v>
+        <v>-5.056048378247951</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-18.11228878080839</v>
       </c>
       <c r="E83">
-        <v>-16.67485322265357</v>
+        <v>-13.4887321227069</v>
       </c>
       <c r="F83">
-        <v>-0.2958010347457804</v>
+        <v>0.1402557079248933</v>
       </c>
       <c r="G83">
-        <v>-6.647622941162427</v>
+        <v>-4.597256424688053</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-18.06777473316603</v>
       </c>
       <c r="E84">
-        <v>-15.79012525577501</v>
+        <v>-14.10737148536875</v>
       </c>
       <c r="F84">
-        <v>-0.4202955433451153</v>
+        <v>-0.00345526768458449</v>
       </c>
       <c r="G84">
-        <v>-6.343718171202871</v>
+        <v>-5.489789433712183</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-17.99089898859214</v>
       </c>
       <c r="E85">
-        <v>-16.84308603203852</v>
+        <v>-15.75832631129315</v>
       </c>
       <c r="F85">
-        <v>-0.05070534434026829</v>
+        <v>-0.2635560052244069</v>
       </c>
       <c r="G85">
-        <v>-7.182295909027959</v>
+        <v>-4.36465749509886</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-17.90754505597763</v>
       </c>
       <c r="E86">
-        <v>-17.41319826723418</v>
+        <v>-16.78595480395775</v>
       </c>
       <c r="F86">
-        <v>-0.4565838341595533</v>
+        <v>-0.3317952551322245</v>
       </c>
       <c r="G86">
-        <v>-6.548144358252867</v>
+        <v>-4.265629146382641</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-17.7968300225076</v>
       </c>
       <c r="E87">
-        <v>-18.68533265699493</v>
+        <v>-17.41560741540626</v>
       </c>
       <c r="F87">
-        <v>-0.004874261045580044</v>
+        <v>-0.2844921629627616</v>
       </c>
       <c r="G87">
-        <v>-5.983782417991151</v>
+        <v>-4.453942908293004</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-17.67994469553581</v>
       </c>
       <c r="E88">
-        <v>-20.86350148384033</v>
+        <v>-18.78080647449865</v>
       </c>
       <c r="F88">
-        <v>-0.5320298804717266</v>
+        <v>-0.3059245127753932</v>
       </c>
       <c r="G88">
-        <v>-7.423495635928179</v>
+        <v>-4.803109456865475</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.54926947538208</v>
       </c>
       <c r="E89">
-        <v>-21.22302156378328</v>
+        <v>-19.65109313776674</v>
       </c>
       <c r="F89">
-        <v>-0.5435267916551809</v>
+        <v>-0.5035497807960768</v>
       </c>
       <c r="G89">
-        <v>-6.579760068152908</v>
+        <v>-4.67803373584627</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.41507631944035</v>
       </c>
       <c r="E90">
-        <v>-24.29649687278916</v>
+        <v>-21.67528479140333</v>
       </c>
       <c r="F90">
-        <v>-0.527434098120995</v>
+        <v>-0.08658607839252888</v>
       </c>
       <c r="G90">
-        <v>-7.25256223809899</v>
+        <v>-4.340159458108253</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.28582581021976</v>
       </c>
       <c r="E91">
-        <v>-24.4399272300341</v>
+        <v>-22.51100561257088</v>
       </c>
       <c r="F91">
-        <v>-0.2108179945251763</v>
+        <v>-0.3606771129982321</v>
       </c>
       <c r="G91">
-        <v>-6.821489482339411</v>
+        <v>-5.130078797597133</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.15950635704923</v>
       </c>
       <c r="E92">
-        <v>-26.66814928008628</v>
+        <v>-25.37242606921957</v>
       </c>
       <c r="F92">
-        <v>-0.2281532391635616</v>
+        <v>-0.4715499480259319</v>
       </c>
       <c r="G92">
-        <v>-7.025667378473961</v>
+        <v>-4.364922338742002</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.05814442464963</v>
       </c>
       <c r="E93">
-        <v>-29.11545437415554</v>
+        <v>-26.4697341914402</v>
       </c>
       <c r="F93">
-        <v>-0.2386511392592397</v>
+        <v>-0.5394056638262534</v>
       </c>
       <c r="G93">
-        <v>-6.58651689159856</v>
+        <v>-5.77110966200283</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.96542024081505</v>
       </c>
       <c r="E94">
-        <v>-30.86760248025534</v>
+        <v>-28.30699043804016</v>
       </c>
       <c r="F94">
-        <v>-0.4903489178650639</v>
+        <v>-0.6157165257069495</v>
       </c>
       <c r="G94">
-        <v>-7.546263906706512</v>
+        <v>-5.412104172087646</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-16.91016576298211</v>
       </c>
       <c r="E95">
-        <v>-31.76382371416536</v>
+        <v>-30.66205504504718</v>
       </c>
       <c r="F95">
-        <v>-0.5500394161759907</v>
+        <v>-0.5879968673070696</v>
       </c>
       <c r="G95">
-        <v>-6.53550469538393</v>
+        <v>-5.777714200353676</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-16.87281839083469</v>
       </c>
       <c r="E96">
-        <v>-35.01921461677036</v>
+        <v>-32.04949796846524</v>
       </c>
       <c r="F96">
-        <v>-0.3133889314420195</v>
+        <v>-0.7543173028085571</v>
       </c>
       <c r="G96">
-        <v>-8.679615929893846</v>
+        <v>-5.835105817822482</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.87164788019428</v>
       </c>
       <c r="E97">
-        <v>-38.00879315207313</v>
+        <v>-35.23895428951856</v>
       </c>
       <c r="F97">
-        <v>-0.224061104193732</v>
+        <v>-0.5764179477507382</v>
       </c>
       <c r="G97">
-        <v>-8.33324348175652</v>
+        <v>-5.267598859298458</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.89731832834448</v>
       </c>
       <c r="E98">
-        <v>-40.47413515811494</v>
+        <v>-37.64088633826797</v>
       </c>
       <c r="F98">
-        <v>-0.9845893585409722</v>
+        <v>-0.63367470263224</v>
       </c>
       <c r="G98">
-        <v>-6.836456458722456</v>
+        <v>-6.023962509201286</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.94795431384452</v>
       </c>
       <c r="E99">
-        <v>-42.44304320106589</v>
+        <v>-39.64872567226286</v>
       </c>
       <c r="F99">
-        <v>-0.3168175441222067</v>
+        <v>-0.6530717537361932</v>
       </c>
       <c r="G99">
-        <v>-7.457941862264296</v>
+        <v>-6.175598737082063</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.03262641048032</v>
       </c>
       <c r="E100">
-        <v>-44.66459707314177</v>
+        <v>-41.81371890398294</v>
       </c>
       <c r="F100">
-        <v>-0.5289491821007153</v>
+        <v>-0.648750989363191</v>
       </c>
       <c r="G100">
-        <v>-8.157427029256906</v>
+        <v>-6.083502670725077</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.1250665763837</v>
       </c>
       <c r="E101">
-        <v>-45.38487350643178</v>
+        <v>-43.61363108967864</v>
       </c>
       <c r="F101">
-        <v>-0.9980130523033381</v>
+        <v>-0.742489044663983</v>
       </c>
       <c r="G101">
-        <v>-8.883194617285788</v>
+        <v>-6.38006796122407</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.26459779763723</v>
       </c>
       <c r="E102">
-        <v>-48.95067205624805</v>
+        <v>-45.39095071855007</v>
       </c>
       <c r="F102">
-        <v>-0.6155491954915839</v>
+        <v>-0.6212889532255818</v>
       </c>
       <c r="G102">
-        <v>-8.29421877093959</v>
+        <v>-6.301214077024169</v>
       </c>
     </row>
   </sheetData>
